--- a/data/PRSMethodPapersGitHub.xlsx
+++ b/data/PRSMethodPapersGitHub.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10719"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophersebastian/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAB4D6C-8ABB-E943-A9BD-CCC48E4215B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C5EF45A-7668-ED45-861B-307B64ACC8AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{28262137-D1CA-8045-A5D2-135F89C25B16}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" firstSheet="3" activeTab="12" xr2:uid="{28262137-D1CA-8045-A5D2-135F89C25B16}"/>
   </bookViews>
   <sheets>
     <sheet name="models" sheetId="1" r:id="rId1"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="236" uniqueCount="108">
   <si>
     <t>Method</t>
   </si>
@@ -175,9 +175,6 @@
     <t>HT</t>
   </si>
   <si>
-    <t>SCZ-MGS</t>
-  </si>
-  <si>
     <t>SCZ-ISC</t>
   </si>
   <si>
@@ -290,9 +287,6 @@
   </si>
   <si>
     <t>Height-Estonian BioBank</t>
-  </si>
-  <si>
-    <t>BMI-H&amp;R Estonian Biobank</t>
   </si>
   <si>
     <t>Diease</t>
@@ -392,6 +386,9 @@
   </si>
   <si>
     <t>asthma</t>
+  </si>
+  <si>
+    <t>BMI- Estonian Biobank</t>
   </si>
 </sst>
 </file>
@@ -876,7 +873,7 @@
         <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="17" x14ac:dyDescent="0.2">
@@ -894,7 +891,7 @@
       <c r="A4" t="s">
         <v>16</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="14" t="s">
         <v>17</v>
       </c>
     </row>
@@ -927,7 +924,7 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C8" t="s">
         <v>24</v>
@@ -997,6 +994,7 @@
     <hyperlink ref="C9" r:id="rId1" xr:uid="{2E593C4D-5D93-674D-8D4D-9BF9FE0A0014}"/>
     <hyperlink ref="C11" r:id="rId2" xr:uid="{44AA4903-90D7-B048-8E13-C22301F5A403}"/>
     <hyperlink ref="C3" r:id="rId3" xr:uid="{5ACF59BF-121A-574D-AD4A-DC0A946EB47D}"/>
+    <hyperlink ref="C4" r:id="rId4" xr:uid="{141BCDDC-0146-5B45-B59A-2D84ED66D94D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
@@ -1024,7 +1022,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B2">
         <v>0.13600000000000001</v>
@@ -1038,7 +1036,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B3">
         <v>0.32200000000000001</v>
@@ -1052,7 +1050,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B4">
         <v>0.122</v>
@@ -1066,7 +1064,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="B5">
         <v>0.32600000000000001</v>
@@ -1104,7 +1102,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B2">
         <v>0.66</v>
@@ -1147,7 +1145,7 @@
         <v>20</v>
       </c>
       <c r="F1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -1192,7 +1190,7 @@
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B4" s="9">
         <v>6.9400000000000003E-2</v>
@@ -1212,7 +1210,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5">
         <v>3.0700000000000002E-2</v>
@@ -1232,7 +1230,7 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="B6">
         <v>5.5300000000000002E-2</v>
@@ -1252,7 +1250,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7">
         <v>3.95E-2</v>
@@ -1272,7 +1270,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B8">
         <v>0.11990000000000001</v>
@@ -1292,7 +1290,7 @@
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B9">
         <v>0.1195</v>
@@ -1312,7 +1310,7 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="B10">
         <v>0.13250000000000001</v>
@@ -1332,7 +1330,7 @@
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B11">
         <v>0.14169999999999999</v>
@@ -1352,7 +1350,7 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B12">
         <v>0.2281</v>
@@ -1372,7 +1370,7 @@
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B13">
         <v>0.14580000000000001</v>
@@ -1392,7 +1390,7 @@
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B14">
         <v>0.1113</v>
@@ -1412,7 +1410,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B15">
         <v>0.1391</v>
@@ -1432,7 +1430,7 @@
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B16">
         <v>0.2616</v>
@@ -1452,7 +1450,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B17">
         <v>0.40629999999999999</v>
@@ -1472,7 +1470,7 @@
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B18">
         <v>0.23330000000000001</v>
@@ -1492,7 +1490,7 @@
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B19">
         <v>0.15190000000000001</v>
@@ -1512,7 +1510,7 @@
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B20">
         <v>0.1676</v>
@@ -1532,7 +1530,7 @@
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B21">
         <v>8.5500000000000007E-2</v>
@@ -1552,7 +1550,7 @@
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B22">
         <v>0.1196</v>
@@ -1627,7 +1625,7 @@
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B2">
         <v>0.57200000000000006</v>
@@ -1662,7 +1660,7 @@
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3">
         <v>0.61599999999999999</v>
@@ -1732,7 +1730,7 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5">
         <v>0.59</v>
@@ -1767,7 +1765,7 @@
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B6">
         <v>0.64400000000000002</v>
@@ -2035,7 +2033,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B2">
         <v>0.627</v>
@@ -2052,7 +2050,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B3">
         <v>0.68300000000000005</v>
@@ -2120,7 +2118,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7">
         <v>0.60099999999999998</v>
@@ -2137,7 +2135,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B8">
         <v>0.61799999999999999</v>
@@ -2154,7 +2152,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B9">
         <v>0.57699999999999996</v>
@@ -2171,7 +2169,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10">
         <v>0.55500000000000005</v>
@@ -2201,7 +2199,7 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="5" t="s">
         <v>5</v>
@@ -2210,12 +2208,12 @@
         <v>16</v>
       </c>
       <c r="D1" s="12" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" s="4" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B2" s="4">
         <v>0.69</v>
@@ -2229,7 +2227,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" s="4" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B3" s="4">
         <v>0.59799999999999998</v>
@@ -2271,7 +2269,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" s="4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B6" s="4">
         <v>0.624</v>
@@ -2312,7 +2310,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B2">
         <v>0.30199999999999999</v>
@@ -2329,7 +2327,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B3">
         <v>0.188</v>
@@ -2346,7 +2344,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B4">
         <v>0.159</v>
@@ -2363,7 +2361,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B5">
         <v>0.14199999999999999</v>
@@ -2380,7 +2378,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B6">
         <v>0.107</v>
@@ -2397,7 +2395,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B7">
         <v>0.13400000000000001</v>
@@ -2414,7 +2412,7 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B8">
         <v>5.2999999999999999E-2</v>
@@ -2431,7 +2429,7 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B9">
         <v>0.113</v>
@@ -2448,7 +2446,7 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B10">
         <v>0.106</v>
@@ -2465,7 +2463,7 @@
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B11">
         <v>8.5999999999999993E-2</v>
@@ -2482,7 +2480,7 @@
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B12">
         <v>8.1000000000000003E-2</v>
@@ -2499,7 +2497,7 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B13">
         <v>0.08</v>
@@ -2516,7 +2514,7 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B14">
         <v>6.0999999999999999E-2</v>
@@ -2533,7 +2531,7 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B15">
         <v>2.5999999999999999E-2</v>
@@ -2550,7 +2548,7 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B16">
         <v>4.2000000000000003E-2</v>
@@ -2567,7 +2565,7 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B17">
         <v>2.4E-2</v>
@@ -2612,7 +2610,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B2">
         <v>0.621</v>
@@ -2668,7 +2666,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B6">
         <v>0.68</v>
@@ -2682,7 +2680,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7">
         <v>0.55700000000000005</v>
@@ -2734,7 +2732,7 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" t="s">
         <v>5</v>
@@ -2745,7 +2743,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B2">
         <v>0.7248</v>
@@ -2756,7 +2754,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B3">
         <v>0.65269999999999995</v>
@@ -2767,7 +2765,7 @@
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B4">
         <v>0.6391</v>
@@ -2778,7 +2776,7 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B5">
         <v>0.625</v>
@@ -2789,7 +2787,7 @@
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6">
         <v>0.56820000000000004</v>
@@ -2822,7 +2820,7 @@
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2">
         <v>8.4099999999999994E-2</v>
@@ -2838,7 +2836,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDB585FA-BB12-D64F-A2CF-C26CE2BD1733}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
@@ -2857,10 +2855,10 @@
         <v>40</v>
       </c>
       <c r="B2">
-        <v>0.7248</v>
+        <v>0.6784</v>
       </c>
       <c r="C2">
-        <v>0.75190000000000001</v>
+        <v>0.71650000000000003</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.2">
@@ -2868,10 +2866,10 @@
         <v>41</v>
       </c>
       <c r="B3">
-        <v>0.6784</v>
+        <v>0.6714</v>
       </c>
       <c r="C3">
-        <v>0.71650000000000003</v>
+        <v>0.69179999999999997</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.2">
@@ -2879,42 +2877,31 @@
         <v>42</v>
       </c>
       <c r="B4">
-        <v>0.6714</v>
+        <v>0.60519999999999996</v>
       </c>
       <c r="C4">
-        <v>0.69179999999999997</v>
+        <v>0.61560000000000004</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B5">
-        <v>0.60519999999999996</v>
+        <v>0.58540000000000003</v>
       </c>
       <c r="C5">
-        <v>0.61560000000000004</v>
+        <v>0.59530000000000005</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6">
-        <v>0.58540000000000003</v>
+        <v>0.55569999999999997</v>
       </c>
       <c r="C6">
-        <v>0.59530000000000005</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A7" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7">
-        <v>0.55569999999999997</v>
-      </c>
-      <c r="C7">
         <v>0.56469999999999998</v>
       </c>
     </row>
@@ -2947,7 +2934,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="8">
         <v>0.64053627504681199</v>
@@ -2981,7 +2968,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" s="8">
         <v>0.55396095450607596</v>
@@ -2998,7 +2985,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B5" s="8">
         <v>0.67894751006986698</v>
@@ -3032,7 +3019,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B7" s="8">
         <v>0.62562324395083202</v>
@@ -3092,7 +3079,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B1" t="s">
         <v>11</v>
@@ -3109,7 +3096,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B2" s="10">
         <v>0.29343871168860902</v>
@@ -3126,7 +3113,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="6" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B3" s="10">
         <v>0.11115073676852601</v>
@@ -3143,7 +3130,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B4" s="10">
         <v>0.10513794170165899</v>
@@ -3160,7 +3147,7 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" s="6" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B5" s="10">
         <v>0.11869647710735701</v>
@@ -3177,7 +3164,7 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B6" s="10">
         <v>0.10045338372303</v>
@@ -3194,7 +3181,7 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B7" s="10">
         <v>7.1245377651020805E-2</v>
@@ -3226,7 +3213,7 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B1" t="s">
         <v>9</v>
@@ -3243,7 +3230,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B2">
         <v>8.0000000000000002E-3</v>
@@ -3277,7 +3264,7 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B4">
         <v>1.2E-2</v>
@@ -3449,7 +3436,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B2">
         <v>0.34899999999999998</v>
@@ -3463,7 +3450,7 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B3">
         <v>0.19900000000000001</v>
@@ -3477,7 +3464,7 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B4">
         <v>0.17399999999999999</v>
@@ -3491,7 +3478,7 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B5">
         <v>0.188</v>
@@ -3505,7 +3492,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B6">
         <v>0.127</v>
@@ -3519,7 +3506,7 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B7">
         <v>0.124</v>
@@ -3533,7 +3520,7 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B8">
         <v>0.11</v>
@@ -3547,7 +3534,7 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B9">
         <v>0.11</v>
@@ -3561,7 +3548,7 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B10">
         <v>0.108</v>
@@ -3575,7 +3562,7 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B11">
         <v>7.3999999999999996E-2</v>
@@ -3589,7 +3576,7 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B12">
         <v>3.9E-2</v>
